--- a/request_forms/048_issue_record_request_form--request_forms.xlsx
+++ b/request_forms/048_issue_record_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>coverage_type</t>
+          <t>coverage_type_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coverage Type</t>
+          <t>Coverage Type 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>claim_status</t>
+          <t>claim_status_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Claim Status</t>
+          <t>Claim Status 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>claim_number</t>
+          <t>claim_number_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Claim Number</t>
+          <t>Claim Number 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -802,9 +802,9 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'auto'}</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Auto'}</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -900,97 +900,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_"workers'_compensation"}</t>
+          <t>workers'_compensation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': "Workers' Compensation"}</t>
+          <t>Workers' Compensation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coverage_type_choices</t>
+          <t>coverage_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'auto'}</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Auto'}</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>coverage_type_choices</t>
+          <t>coverage_type_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>coverage_type_choices</t>
+          <t>coverage_type_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>coverage_type_choices</t>
+          <t>coverage_type_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>coverage_type_choices</t>
+          <t>coverage_type_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_"workers'_compensation"}</t>
+          <t>workers'_compensation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': "Workers' Compensation"}</t>
+          <t>Workers' Compensation</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1036,63 +1036,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>claim_status_choices</t>
+          <t>claim_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>claim_status_choices</t>
+          <t>claim_status_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>claim_status_choices</t>
+          <t>claim_status_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
